--- a/crates/xlstream-eval/tests/fixtures/lookup/vlookup.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/lookup/vlookup.xlsx
@@ -21,12 +21,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
-  <si>
-    <t xml:space="preserve">region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vlookup</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+  <si>
+    <t xml:space="preserve">key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vlookup_val</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vlookup_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vlookup_miss</t>
   </si>
   <si>
     <t xml:space="preserve">EMEA</t>
@@ -38,6 +44,15 @@
     <t xml:space="preserve">AMER</t>
   </si>
   <si>
+    <t xml:space="preserve">LATAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZZZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Europe</t>
   </si>
   <si>
@@ -47,13 +62,7 @@
     <t xml:space="preserve">Americas</t>
   </si>
   <si>
-    <t xml:space="preserve">LATAM</t>
-  </si>
-  <si>
     <t xml:space="preserve">LatAm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEA</t>
   </si>
   <si>
     <t xml:space="preserve">MidEast</t>
@@ -329,7 +338,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -339,95 +348,147 @@
       <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="0" t="str">
+        <v>4</v>
+      </c>
+      <c r="B2" s="0" t="n">
         <f aca="false">VLOOKUP(A2,Lookup1!A:C,2,FALSE())</f>
+        <v>100</v>
+      </c>
+      <c r="C2" s="0" t="str">
+        <f aca="false">VLOOKUP(A2,Lookup1!A:C,3,FALSE())</f>
         <v>Europe</v>
+      </c>
+      <c r="D2" s="0" t="str">
+        <f aca="false">IFERROR(VLOOKUP("NOPE",Lookup1!A:C,2,FALSE()),"miss")</f>
+        <v>miss</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B3" s="0" t="n">
         <f aca="false">VLOOKUP(A3,Lookup1!A:C,2,FALSE())</f>
+        <v>200</v>
+      </c>
+      <c r="C3" s="0" t="str">
+        <f aca="false">VLOOKUP(A3,Lookup1!A:C,3,FALSE())</f>
         <v>Asia</v>
+      </c>
+      <c r="D3" s="0" t="str">
+        <f aca="false">IFERROR(VLOOKUP("NOPE",Lookup1!A:C,2,FALSE()),"miss")</f>
+        <v>miss</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="0" t="str">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="n">
         <f aca="false">VLOOKUP(A4,Lookup1!A:C,2,FALSE())</f>
+        <v>300</v>
+      </c>
+      <c r="C4" s="0" t="str">
+        <f aca="false">VLOOKUP(A4,Lookup1!A:C,3,FALSE())</f>
         <v>Americas</v>
+      </c>
+      <c r="D4" s="0" t="str">
+        <f aca="false">IFERROR(VLOOKUP("NOPE",Lookup1!A:C,2,FALSE()),"miss")</f>
+        <v>miss</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="0" t="str">
+        <v>7</v>
+      </c>
+      <c r="B5" s="0" t="n">
         <f aca="false">VLOOKUP(A5,Lookup1!A:C,2,FALSE())</f>
-        <v>Europe</v>
+        <v>400</v>
+      </c>
+      <c r="C5" s="0" t="str">
+        <f aca="false">VLOOKUP(A5,Lookup1!A:C,3,FALSE())</f>
+        <v>LatAm</v>
+      </c>
+      <c r="D5" s="0" t="str">
+        <f aca="false">IFERROR(VLOOKUP("NOPE",Lookup1!A:C,2,FALSE()),"miss")</f>
+        <v>miss</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="0" t="str">
+        <v>8</v>
+      </c>
+      <c r="B6" s="0" t="n">
         <f aca="false">VLOOKUP(A6,Lookup1!A:C,2,FALSE())</f>
-        <v>Asia</v>
+        <v>500</v>
+      </c>
+      <c r="C6" s="0" t="str">
+        <f aca="false">VLOOKUP(A6,Lookup1!A:C,3,FALSE())</f>
+        <v>MidEast</v>
+      </c>
+      <c r="D6" s="0" t="str">
+        <f aca="false">IFERROR(VLOOKUP("NOPE",Lookup1!A:C,2,FALSE()),"miss")</f>
+        <v>miss</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="0" t="str">
+      <c r="B7" s="0" t="n">
         <f aca="false">VLOOKUP(A7,Lookup1!A:C,2,FALSE())</f>
-        <v>Americas</v>
+        <v>100</v>
+      </c>
+      <c r="C7" s="0" t="str">
+        <f aca="false">VLOOKUP(A7,Lookup1!A:C,3,FALSE())</f>
+        <v>Europe</v>
+      </c>
+      <c r="D7" s="0" t="str">
+        <f aca="false">IFERROR(VLOOKUP("NOPE",Lookup1!A:C,2,FALSE()),"miss")</f>
+        <v>miss</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="0" t="str">
+        <v>9</v>
+      </c>
+      <c r="B8" s="0" t="e">
         <f aca="false">VLOOKUP(A8,Lookup1!A:C,2,FALSE())</f>
-        <v>Europe</v>
+        <v>#N/A</v>
+      </c>
+      <c r="C8" s="0" t="e">
+        <f aca="false">VLOOKUP(A8,Lookup1!A:C,3,FALSE())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D8" s="0" t="str">
+        <f aca="false">IFERROR(VLOOKUP("NOPE",Lookup1!A:C,2,FALSE()),"miss")</f>
+        <v>miss</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="0" t="str">
+        <v>5</v>
+      </c>
+      <c r="B9" s="0" t="n">
         <f aca="false">VLOOKUP(A9,Lookup1!A:C,2,FALSE())</f>
+        <v>200</v>
+      </c>
+      <c r="C9" s="0" t="str">
+        <f aca="false">VLOOKUP(A9,Lookup1!A:C,3,FALSE())</f>
         <v>Asia</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="0" t="str">
-        <f aca="false">VLOOKUP(A10,Lookup1!A:C,2,FALSE())</f>
-        <v>Americas</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="0" t="str">
-        <f aca="false">VLOOKUP(A11,Lookup1!A:C,2,FALSE())</f>
-        <v>Europe</v>
+      <c r="D9" s="0" t="str">
+        <f aca="false">IFERROR(VLOOKUP("NOPE",Lookup1!A:C,2,FALSE()),"miss")</f>
+        <v>miss</v>
       </c>
     </row>
   </sheetData>
@@ -451,57 +512,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B1" s="0" t="n">
         <v>100</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" s="0" t="n">
         <v>200</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" s="0" t="n">
         <v>300</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>50</v>
+        <v>7</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>75</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
